--- a/business_forms/016_self_evaluation--business_forms.xlsx
+++ b/business_forms/016_self_evaluation--business_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>company_performance</t>
+          <t>Job Performance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,10 +538,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_your_job_title</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your job title?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter your job title</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,7 +565,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>Job strengths and weaknesses</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +583,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>self_evaluation_question_2</t>
+          <t>self_evaluation_page_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_is_your_job_title</t>
+          <t>Job Satisfaction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +606,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>self_evaluation_answer_2</t>
+          <t>self_evaluation_question_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>How satisfied are you with your job?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +629,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>self_evaluation_page_2</t>
+          <t>self_evaluation_page_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>Team Satisfaction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>How satisfied are you with your team?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +675,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>self_evaluation_answer_3</t>
+          <t>self_evaluation_page_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>Leadership Satisfaction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +703,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_is_your_job_title</t>
+          <t>How satisfied are you with your leadership?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +721,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>self_evaluation_answer_4</t>
+          <t>self_evaluation_page_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>answer_4</t>
+          <t>Growth Opportunities</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,12 +744,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>self_evaluation_page_3</t>
+          <t>self_evaluation_question_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>team_satisfaction</t>
+          <t>What growth opportunities would you like to see in your role?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -763,12 +767,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>self_evaluation_question_5</t>
+          <t>self_evaluation_page_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>team_satisfaction</t>
+          <t>Performance Review</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +790,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>self_evaluation_answer_5</t>
+          <t>self_evaluation_question_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>answer_5</t>
+          <t>How do you rate your performance in terms of meeting your goals?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +813,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>self_evaluation_question_6</t>
+          <t>self_evaluation_page_7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>what_is_your_job_title</t>
+          <t>Challenges</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +836,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>self_evaluation_answer_6</t>
+          <t>self_evaluation_question_7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>answer_6</t>
+          <t>What challenges do you face in your work?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,12 +859,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>self_evaluation_page_4</t>
+          <t>self_evaluation_page_8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leadership_satisfaction</t>
+          <t>Job Satisfaction (scale)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +882,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>self_evaluation_question_7</t>
+          <t>self_evaluation_page_9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>leadership_satisfaction</t>
+          <t>Enjoyment</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +905,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>self_evaluation_answer_7</t>
+          <t>self_evaluation_question_8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>answer_7</t>
+          <t>What areas of your job do you enjoy the most?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +928,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>self_evaluation_question_8</t>
+          <t>self_evaluation_page_10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>what_is_your_job_title</t>
+          <t>Dislike</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,131 +951,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>self_evaluation_answer_8</t>
+          <t>self_evaluation_question_9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>answer_8</t>
+          <t>What areas of your job do you dislike the most?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>self_evaluation_page_5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>growth_opportunities</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>self_evaluation_question_9</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>growth_opportunities</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>self_evaluation_answer_9</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>answer_9</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>self_evaluation_question_10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>what_is_your_job_title</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>self_evaluation_answer_10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>answer_10</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
